--- a/input.xlsx
+++ b/input.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12525"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="数据" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="56">
   <si>
     <t>所在分行</t>
   </si>
@@ -191,13 +191,10 @@
     <t>610303198905231635</t>
   </si>
   <si>
-    <t>股东1</t>
-  </si>
-  <si>
-    <t>股东2</t>
-  </si>
-  <si>
-    <t>股东3</t>
+    <t>股东</t>
+  </si>
+  <si>
+    <t>金老肥</t>
   </si>
 </sst>
 </file>
@@ -882,13 +879,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1213,7 +1203,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -1452,21 +1442,19 @@
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:B10 A11 A12:B31" numberStoredAsText="1"/>
+    <ignoredError sqref="A12:B28 B29 A11 A1:B10" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/input.xlsx
+++ b/input.xlsx
@@ -3,8 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="93W30xZmeaWoyQHhdWD1CUP+UIQpXABt4q6/+O+s3zV3qfMT+Bxr5YxM3nCreaUPetyikjqEoe+UIIXFpBNCQA==" workbookSaltValue="jUPv19cqXwEoSDjuy9rXPA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowWidth="13545" windowHeight="12525"/>
   </bookViews>
   <sheets>
     <sheet name="数据" sheetId="1" r:id="rId1"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
   <si>
     <t>所在分行</t>
   </si>
@@ -135,6 +136,21 @@
   </si>
   <si>
     <t>陕西省西安市国际港务区港务大道9号陆港大厦A座2016室</t>
+  </si>
+  <si>
+    <t>企业成立时间</t>
+  </si>
+  <si>
+    <t>2020-10-20</t>
+  </si>
+  <si>
+    <t>企业持续经营时间</t>
+  </si>
+  <si>
+    <t>企业经营范围和主营业务</t>
+  </si>
+  <si>
+    <t>金属及金属矿批发</t>
   </si>
   <si>
     <t>企业法人</t>
@@ -207,9 +223,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -670,155 +693,173 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -879,6 +920,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1203,258 +1251,307 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
+  <dimension ref="A1:D33"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="58.875" customWidth="1"/>
+    <col min="1" max="1" width="28" style="1" customWidth="1"/>
+    <col min="2" max="2" width="58.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30.375" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="2">
         <v>150102004.26</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" t="s">
+      <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" t="s">
+      <c r="A18" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" t="s">
+      <c r="A19" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
+    <row r="20" spans="1:4">
+      <c r="A20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="3" t="s">
         <v>37</v>
       </c>
+      <c r="D20" s="4"/>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" t="s">
+      <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="5">
+        <f ca="1">YEAR(TODAY())-YEAR(B20)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
+      <c r="B22" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B22" t="s">
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
+      <c r="B23" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B23" t="s">
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
+      <c r="B24" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B24" t="s">
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
+      <c r="B25" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B25" t="s">
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
+      <c r="B26" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B26" t="s">
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
+      <c r="B27" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B27" t="s">
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
+      <c r="B28" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B28" t="s">
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
+      <c r="B29" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B29" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>54</v>
-      </c>
-      <c r="B30" t="s">
+      <c r="A30" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="B30" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
+  <protectedRanges>
+    <protectedRange password="9690" sqref="A1:B41 B21 D20" name="区域1" securityDescriptor="O:WDG:WDD:"/>
+  </protectedRanges>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A12:B28 B29 A11 A1:B10" numberStoredAsText="1"/>
+    <ignoredError sqref="B19 A18:B18 B17 A15:B16 B14 A12:B13 A11 A1:B10 B28:B31 B26 A24:B25" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<allowEditUser xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" hasInvisiblePropRange="0">
+  <rangeList sheetStid="1" master="" otherUserPermission="visible">
+    <arrUserId title="区域1" rangeCreator="" othersAccessPermission="edit"/>
+  </rangeList>
+</allowEditUser>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A5607D9-04D2-4DE1-AC0E-A7772F01BC71}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/input.xlsx
+++ b/input.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="93W30xZmeaWoyQHhdWD1CUP+UIQpXABt4q6/+O+s3zV3qfMT+Bxr5YxM3nCreaUPetyikjqEoe+UIIXFpBNCQA==" workbookSaltValue="jUPv19cqXwEoSDjuy9rXPA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView windowWidth="13545" windowHeight="12525"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="数据" sheetId="1" r:id="rId1"/>
@@ -28,12 +28,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="60">
   <si>
     <t>所在分行</t>
   </si>
   <si>
-    <t>北平分行</t>
+    <t>西安分行</t>
   </si>
   <si>
     <t>分行地址</t>
@@ -160,9 +160,6 @@
   </si>
   <si>
     <t>企业法人电话</t>
-  </si>
-  <si>
-    <t>13991107458</t>
   </si>
   <si>
     <t>保证金账户</t>
@@ -838,7 +835,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
       <protection locked="0"/>
@@ -859,6 +856,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -920,13 +921,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1346,7 +1340,7 @@
         <v>19</v>
       </c>
       <c r="B11" s="2">
-        <v>150102004.26</v>
+        <v>150000000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1389,7 +1383,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
@@ -1397,7 +1391,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
         <v>32</v>
       </c>
@@ -1405,7 +1399,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
         <v>34</v>
       </c>
@@ -1422,7 +1416,7 @@
       </c>
       <c r="D20" s="4"/>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -1431,7 +1425,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1439,7 +1433,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
         <v>41</v>
       </c>
@@ -1447,73 +1441,73 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="7">
+        <v>13991107458</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="1" t="s">
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B26" s="1" t="s">
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B27" s="1" t="s">
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="1" t="s">
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B29" s="1" t="s">
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="1" t="s">
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="1" t="s">
+      <c r="B31" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B31" s="1" t="s">
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="1" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>42</v>
@@ -1521,10 +1515,10 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1534,7 +1528,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="B19 A18:B18 B17 A15:B16 B14 A12:B13 A11 A1:B10 B28:B31 B26 A24:B25" numberStoredAsText="1"/>
+    <ignoredError sqref="A24 A25:B25 B26 B28:B31 A1 A2:B3 A4:A5 A6:B10 A11 A12:B13 B14 A15:B16 B17 A18:B18 B19" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
